--- a/data/flow_2026/2026-06-09.xlsx
+++ b/data/flow_2026/2026-06-09.xlsx
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10615</v>
+        <v>10627</v>
       </c>
       <c r="C2" t="n">
-        <v>12201316692</v>
+        <v>12235752575</v>
       </c>
       <c r="D2" t="n">
         <v>1805241938</v>
